--- a/docs/downloads/04/tbl_other_act_all_alaotra_mangabe.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_alaotra_mangabe.xlsx
@@ -405,12 +405,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -459,12 +453,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -477,12 +465,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +477,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -531,12 +507,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -567,12 +537,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -585,12 +549,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -603,12 +561,6 @@
           <t>Tisseur (Mpandrary) avec des brins végétaux (nattes, soubiques,chapeaux...),tresseur(vannerie),Fileur (sisalerie) - Mpandrary tsihy, sobika, satroka, tsihy, mpanao tady</t>
         </is>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -634,12 +586,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +598,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +610,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,12 +622,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +634,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +646,6 @@
           <t>Coiffeur-Mpanety, mpanao volo</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,12 +658,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -778,12 +688,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -796,12 +700,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,12 +712,6 @@
           <t>Cueillette (produit naturel ou collecte sauvage) - Mpioty vokatra voajanahary, tsy nambolena</t>
         </is>
       </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -850,12 +742,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -904,12 +790,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -940,12 +820,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C33">
-        <v>3</v>
-      </c>
-      <c r="D33">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -958,12 +832,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -994,12 +862,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
-      <c r="D36">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1012,12 +874,6 @@
           <t>Gardien, agent de sécurité (privé), concierge - Mpiambina, Mpiandraikitra ny fandriampahalemana, Mpandray olona</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1066,12 +922,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1102,12 +952,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1156,12 +1000,6 @@
           <t>Potier, Mouleur de brique et de tuile à la main Mpanamboatra tavim-boninkazo, biriky, taila amin?ny tanana</t>
         </is>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1174,12 +1012,6 @@
           <t>Pépiniériste,Horticulteur (plantesd'ornement), fleuriste - Mpikarakara zanakazo, Mpamboly voninkazo</t>
         </is>
       </c>
-      <c r="C46">
-        <v>2</v>
-      </c>
-      <c r="D46">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1192,12 +1024,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C47">
-        <v>3</v>
-      </c>
-      <c r="D47">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1210,12 +1036,6 @@
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
       </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-      <c r="D48">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1245,12 +1065,6 @@
         <is>
           <t>Taxi-bicyclette</t>
         </is>
-      </c>
-      <c r="C50">
-        <v>2</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
       </c>
     </row>
     <row r="51">
